--- a/export_nesparovane_platby.xlsx
+++ b/export_nesparovane_platby.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="qry_Nesparovane_Platby"/>
   </sheets>
   <definedNames>
-    <definedName name="qry_Nesparovane_Platby">'qry_Nesparovane_Platby'!$A$1:$G$183</definedName>
+    <definedName name="qry_Nesparovane_Platby">'qry_Nesparovane_Platby'!$A$1:$H$139</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -372,20 +372,25 @@
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
+          <t>Skratka</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
           <t>var_symbol_banka</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>iban_protistrany</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>nazov_protistrany</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>FK_faktura</t>
         </is>
@@ -393,25 +398,30 @@
     </row>
     <row outlineLevel="0" r="2">
       <c r="A2" s="0">
-        <v>4201</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1">
         <v>46030</v>
       </c>
       <c r="C2" s="2">
-        <v>7700</v>
+        <v>8900</v>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>1192026</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
+          <t>1292O26</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
           <t>CZ2601000000000000000019</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>Alza.cz a.s.</t>
         </is>
@@ -419,51 +429,61 @@
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="0">
-        <v>4199</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1">
         <v>46030</v>
       </c>
       <c r="C3" s="2">
-        <v>600</v>
+        <v>-45.9</v>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>20260004</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>UHRADA75</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="0">
-        <v>4192</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="C4" s="2">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>UHRADA37</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
+          <t>20260007</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
           <t>SK8009000000000000000010</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
@@ -471,545 +491,646 @@
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="0">
-        <v>4204</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="C5" s="2">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>20260008</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>2O260027</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="0">
-        <v>4198</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1">
-        <v>46032</v>
+        <v>46036</v>
       </c>
       <c r="C6" s="2">
-        <v>-45.9</v>
+        <v>400</v>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>316359O3</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>2O260003</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="0">
-        <v>4215</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
-        <v>46032</v>
+        <v>46036</v>
       </c>
       <c r="C7" s="2">
-        <v>850</v>
+        <v>-45.9</v>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>2O260028</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>UHRADA37</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="0">
-        <v>4203</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1">
-        <v>46033</v>
+        <v>46037</v>
       </c>
       <c r="C8" s="2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>UHRADA49</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>20260030</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="0">
-        <v>4195</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>46033</v>
+        <v>46037</v>
       </c>
       <c r="C9" s="2">
-        <v>150</v>
+        <v>2100</v>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>2O26002</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>2O260031</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="0">
-        <v>4197</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1">
-        <v>46033</v>
+        <v>46039</v>
       </c>
       <c r="C10" s="2">
-        <v>850</v>
+        <v>175</v>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>2O260002</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260032</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="0">
-        <v>4202</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1">
-        <v>46035</v>
+        <v>46043</v>
       </c>
       <c r="C11" s="2">
-        <v>7700</v>
+        <v>600</v>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>1192026</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
+          <t>20260007</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>Alza.cz a.s.</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="0">
-        <v>4223</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="C12" s="2">
-        <v>225</v>
+        <v>329.12</v>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>20260033</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260120001</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="0">
-        <v>4220</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1">
-        <v>46037</v>
+        <v>46045</v>
       </c>
       <c r="C13" s="2">
-        <v>1050</v>
+        <v>1321.21</v>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>20260031</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>2O260122198</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="0">
-        <v>4228</v>
+        <v>46</v>
       </c>
       <c r="B14" s="1">
-        <v>46040</v>
+        <v>46047</v>
       </c>
       <c r="C14" s="2">
-        <v>1500</v>
+        <v>436.69</v>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>UHRADA6</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
+          <t>2O260122006</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>Alza.cz a.s.</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="0">
-        <v>4229</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1">
-        <v>46041</v>
+        <v>46047</v>
       </c>
       <c r="C15" s="2">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>20260036</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>20260030</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="0">
-        <v>4227</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="C16" s="2">
-        <v>1200</v>
+        <v>-234.22</v>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>UHRADA50</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>2O260122200</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="0">
-        <v>4230</v>
+        <v>52</v>
       </c>
       <c r="B17" s="1">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="C17" s="2">
-        <v>550</v>
+        <v>268.56</v>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>20260037</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260123011</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="0">
-        <v>4219</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1">
-        <v>46041</v>
+        <v>46049</v>
       </c>
       <c r="C18" s="2">
-        <v>1200</v>
+        <v>260.03</v>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>UHRADA49</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>UHRADA54</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="0">
-        <v>4205</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="C19" s="2">
-        <v>550</v>
+        <v>-7.5</v>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>20260008</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F19" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
+          <t>POPLATOK 01/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>Mesačný poplatok za účet</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="0">
-        <v>4200</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="C20" s="2">
-        <v>600</v>
+        <v>175</v>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>20260004</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260032</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="0">
-        <v>4240</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="C21" s="2">
-        <v>-337.04</v>
+        <v>498.73</v>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>UHRADA24</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>UHRADA10</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="0">
-        <v>4242</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="C22" s="2">
-        <v>209.82</v>
+        <v>-1185.47</v>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>20260121003</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>UHRADA60</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="0">
-        <v>4241</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1">
-        <v>46044</v>
+        <v>46051</v>
       </c>
       <c r="C23" s="2">
-        <v>64.34</v>
+        <v>-259.54</v>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>20260121197</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>2O260122008</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="0">
-        <v>4218</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="C24" s="2">
-        <v>3200</v>
+        <v>1220.07</v>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>1122O26</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
+          <t>20260127017</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>Alza.cz a.s.</t>
+          <t>SK731100000818630575</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="0">
-        <v>4233</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1">
-        <v>46044</v>
+        <v>46053</v>
       </c>
       <c r="C25" s="2">
-        <v>329.12</v>
+        <v>329.13</v>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
           <t>20260120001</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>SK3309000000000000000011</t>
         </is>
       </c>
-      <c r="F25" s="0" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>Flux a.s.</t>
         </is>
@@ -1017,358 +1138,433 @@
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="0">
-        <v>4226</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1">
-        <v>46045</v>
+        <v>46053</v>
       </c>
       <c r="C26" s="2">
-        <v>-120</v>
+        <v>903.98</v>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>3367O3</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>2O260129215</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="0">
-        <v>4238</v>
+        <v>42</v>
       </c>
       <c r="B27" s="1">
-        <v>46045</v>
+        <v>46053</v>
       </c>
       <c r="C27" s="2">
-        <v>1018.43</v>
+        <v>128.68</v>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>2O260121195</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>2O260121197</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="0">
-        <v>4224</v>
+        <v>58</v>
       </c>
       <c r="B28" s="1">
-        <v>46046</v>
+        <v>46053</v>
       </c>
       <c r="C28" s="2">
-        <v>225</v>
+        <v>-787.16</v>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>20260033</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260127208</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="0">
-        <v>4231</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1">
-        <v>46046</v>
+        <v>46055</v>
       </c>
       <c r="C29" s="2">
-        <v>550</v>
+        <v>1468.48</v>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>20260037</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>2O260123202</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="0">
-        <v>4244</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1">
-        <v>46046</v>
+        <v>46055</v>
       </c>
       <c r="C30" s="2">
-        <v>436.69</v>
+        <v>-838.67</v>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>2O260122006</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260127016</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="0">
-        <v>4251</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1">
-        <v>46047</v>
+        <v>46055</v>
       </c>
       <c r="C31" s="2">
-        <v>268.56</v>
+        <v>-191.63</v>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>20260123011</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260126012</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="0">
-        <v>4254</v>
+        <v>72</v>
       </c>
       <c r="B32" s="1">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="C32" s="2">
-        <v>-592.74</v>
+        <v>839.13</v>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>20260126204</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>2O260126206</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="0">
-        <v>4235</v>
+        <v>86</v>
       </c>
       <c r="B33" s="1">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="C33" s="2">
-        <v>1509.87</v>
+        <v>286.82</v>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>2O260120194</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260129023</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="0">
-        <v>4259</v>
+        <v>71</v>
       </c>
       <c r="B34" s="1">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="C34" s="2">
-        <v>533.79</v>
+        <v>419.84</v>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>20260127209</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>2O260126205</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="0">
-        <v>4266</v>
+        <v>106</v>
       </c>
       <c r="B35" s="1">
-        <v>46050</v>
+        <v>46059</v>
       </c>
       <c r="C35" s="2">
-        <v>-7.5</v>
+        <v>171.82</v>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>POPLATOK 01/2026</t>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>20260203222</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t>Mesačný poplatok za účet</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="0">
-        <v>4261</v>
+        <v>93</v>
       </c>
       <c r="B36" s="1">
-        <v>46051</v>
+        <v>46059</v>
       </c>
       <c r="C36" s="2">
-        <v>419.52</v>
+        <v>1337.82</v>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>20260128212</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
+          <t>20260130217</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t>Alza.cz a.s.</t>
+          <t>SK791100000573851942</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="37">
       <c r="A37" s="0">
-        <v>4260</v>
+        <v>88</v>
       </c>
       <c r="B37" s="1">
-        <v>46052</v>
+        <v>46060</v>
       </c>
       <c r="C37" s="2">
-        <v>586.58</v>
+        <v>1448.82</v>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>2O260128211</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260129214</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="38">
       <c r="A38" s="0">
-        <v>4221</v>
+        <v>119</v>
       </c>
       <c r="B38" s="1">
-        <v>46052</v>
+        <v>46060</v>
       </c>
       <c r="C38" s="2">
-        <v>1050</v>
+        <v>763.61</v>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>20260031</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260204225</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="0">
-        <v>4256</v>
+        <v>117</v>
       </c>
       <c r="B39" s="1">
-        <v>46052</v>
+        <v>46061</v>
       </c>
       <c r="C39" s="2">
-        <v>169.32</v>
+        <v>341</v>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>20260127015</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
+          <t>20260204226</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
           <t>SK7809000000000000000021</t>
         </is>
       </c>
-      <c r="F39" s="0" t="inlineStr">
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>Jana Tvorivá - Creative Studio</t>
         </is>
@@ -1376,103 +1572,123 @@
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="0">
-        <v>4257</v>
+        <v>69</v>
       </c>
       <c r="B40" s="1">
-        <v>46052</v>
+        <v>46062</v>
       </c>
       <c r="C40" s="2">
-        <v>1220.07</v>
+        <v>268.55</v>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>20260127017</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260123011</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="0">
-        <v>4234</v>
+        <v>125</v>
       </c>
       <c r="B41" s="1">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="C41" s="2">
-        <v>329.13</v>
+        <v>585.33</v>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>20260120001</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>2O260205038</t>
         </is>
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="0">
-        <v>4253</v>
+        <v>109</v>
       </c>
       <c r="B42" s="1">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="C42" s="2">
-        <v>-191.63</v>
+        <v>726.74</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>UHRADA7</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260203030</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="0">
-        <v>4265</v>
+        <v>131</v>
       </c>
       <c r="B43" s="1">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="C43" s="2">
-        <v>-222.52</v>
+        <v>-302.1</v>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>2O260130216</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
+          <t>20260206040</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="inlineStr">
+        <is>
           <t>SK9509000000000000000006</t>
         </is>
       </c>
-      <c r="F43" s="0" t="inlineStr">
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>KROS a.s.</t>
         </is>
@@ -1480,415 +1696,495 @@
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="0">
-        <v>4264</v>
+        <v>122</v>
       </c>
       <c r="B44" s="1">
-        <v>46053</v>
+        <v>46063</v>
       </c>
       <c r="C44" s="2">
-        <v>861.19</v>
+        <v>1091.92</v>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>UHRADA54</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>2O260205230</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="0">
-        <v>4286</v>
+        <v>114</v>
       </c>
       <c r="B45" s="1">
-        <v>46054</v>
+        <v>46063</v>
       </c>
       <c r="C45" s="2">
-        <v>451.99</v>
+        <v>450</v>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>20260129215</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>2O260039</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="0">
-        <v>4290</v>
+        <v>101</v>
       </c>
       <c r="B46" s="1">
-        <v>46054</v>
+        <v>46063</v>
       </c>
       <c r="C46" s="2">
-        <v>724.41</v>
+        <v>193</v>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>20260129214</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260202219</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="0">
-        <v>4293</v>
+        <v>87</v>
       </c>
       <c r="B47" s="1">
-        <v>46054</v>
+        <v>46063</v>
       </c>
       <c r="C47" s="2">
-        <v>62.9</v>
+        <v>286.81</v>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>20260130025</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260129023</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="0">
-        <v>4274</v>
+        <v>142</v>
       </c>
       <c r="B48" s="1">
-        <v>46054</v>
+        <v>46066</v>
       </c>
       <c r="C48" s="2">
-        <v>419.84</v>
+        <v>570.78</v>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>UHRADA51</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>UHRADA31</t>
         </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="0">
-        <v>4296</v>
+        <v>159</v>
       </c>
       <c r="B49" s="1">
-        <v>46055</v>
+        <v>46066</v>
       </c>
       <c r="C49" s="2">
-        <v>-417.62</v>
+        <v>1515.81</v>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>20260130024</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>2O260212051</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="0">
-        <v>4288</v>
+        <v>75</v>
       </c>
       <c r="B50" s="1">
-        <v>46055</v>
+        <v>46067</v>
       </c>
       <c r="C50" s="2">
-        <v>1034.51</v>
+        <v>-787.17</v>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>2O260129022</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260127208</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="0">
-        <v>4278</v>
+        <v>136</v>
       </c>
       <c r="B51" s="1">
-        <v>46056</v>
+        <v>46067</v>
       </c>
       <c r="C51" s="2">
-        <v>652.17</v>
+        <v>1468.62</v>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>UHRADA12</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260209234</t>
         </is>
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="0">
-        <v>4292</v>
+        <v>120</v>
       </c>
       <c r="B52" s="1">
-        <v>46056</v>
+        <v>46067</v>
       </c>
       <c r="C52" s="2">
-        <v>644.81</v>
+        <v>763.61</v>
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>2O260129213</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>20260204225</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="0">
-        <v>4306</v>
+        <v>148</v>
       </c>
       <c r="B53" s="1">
-        <v>46057</v>
+        <v>46068</v>
       </c>
       <c r="C53" s="2">
-        <v>1325.07</v>
+        <v>1200</v>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>20260202221</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260043</t>
         </is>
       </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="0">
-        <v>4268</v>
+        <v>107</v>
       </c>
       <c r="B54" s="1">
-        <v>46059</v>
+        <v>46068</v>
       </c>
       <c r="C54" s="2">
-        <v>64.34</v>
+        <v>171.81</v>
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>20260121197</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260203222</t>
         </is>
       </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="0">
-        <v>4294</v>
+        <v>102</v>
       </c>
       <c r="B55" s="1">
-        <v>46059</v>
+        <v>46068</v>
       </c>
       <c r="C55" s="2">
-        <v>62.91</v>
+        <v>1325.07</v>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>20260130025</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260202221</t>
         </is>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="0">
-        <v>4320</v>
+        <v>64</v>
       </c>
       <c r="B56" s="1">
-        <v>46060</v>
+        <v>46069</v>
       </c>
       <c r="C56" s="2">
-        <v>341</v>
+        <v>550</v>
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>20260204226</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>20260037</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="0">
-        <v>4305</v>
+        <v>144</v>
       </c>
       <c r="B57" s="1">
-        <v>46060</v>
+        <v>46069</v>
       </c>
       <c r="C57" s="2">
-        <v>193</v>
+        <v>256.2</v>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>2O260202219</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260210237</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="58">
       <c r="A58" s="0">
-        <v>4330</v>
+        <v>138</v>
       </c>
       <c r="B58" s="1">
-        <v>46060</v>
+        <v>46069</v>
       </c>
       <c r="C58" s="2">
-        <v>641.88</v>
+        <v>717.1</v>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>20260206231</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260209043</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="0">
-        <v>4315</v>
+        <v>110</v>
       </c>
       <c r="B59" s="1">
-        <v>46060</v>
+        <v>46069</v>
       </c>
       <c r="C59" s="2">
-        <v>717.54</v>
+        <v>726.75</v>
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>20260204033</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
+          <t>20260203030</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
           <t>SK481100000332819938</t>
         </is>
       </c>
-      <c r="F59" s="0" t="inlineStr">
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>Lucia Prekladová - LINGUA</t>
         </is>
@@ -1896,103 +2192,123 @@
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="0">
-        <v>4332</v>
+        <v>162</v>
       </c>
       <c r="B60" s="1">
-        <v>46060</v>
+        <v>46070</v>
       </c>
       <c r="C60" s="2">
-        <v>490.94</v>
+        <v>297.41</v>
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>20260206041</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>2O260213246</t>
         </is>
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="0">
-        <v>4334</v>
+        <v>63</v>
       </c>
       <c r="B61" s="1">
-        <v>46060</v>
+        <v>46070</v>
       </c>
       <c r="C61" s="2">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>20260041</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>1152026</t>
         </is>
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="0">
-        <v>4267</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>46060</v>
+        <v>46070</v>
       </c>
       <c r="C62" s="2">
-        <v>150</v>
+        <v>1038.57</v>
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>20260036</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>20260209042</t>
         </is>
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="0">
-        <v>4289</v>
+        <v>169</v>
       </c>
       <c r="B63" s="1">
-        <v>46061</v>
+        <v>46073</v>
       </c>
       <c r="C63" s="2">
-        <v>742.01</v>
+        <v>998.95</v>
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>2O260129021</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
+          <t>UHRADA68</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
           <t>SK7809000000000000000021</t>
         </is>
       </c>
-      <c r="F63" s="0" t="inlineStr">
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>Jana Tvorivá - Creative Studio</t>
         </is>
@@ -2000,77 +2316,92 @@
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="0">
-        <v>4323</v>
+        <v>160</v>
       </c>
       <c r="B64" s="1">
-        <v>46061</v>
+        <v>46073</v>
       </c>
       <c r="C64" s="2">
-        <v>350</v>
+        <v>-1122</v>
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>2O260040</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>2O260212244</t>
         </is>
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="0">
-        <v>4295</v>
+        <v>132</v>
       </c>
       <c r="B65" s="1">
-        <v>46062</v>
+        <v>46074</v>
       </c>
       <c r="C65" s="2">
-        <v>1337.82</v>
+        <v>-302.1</v>
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>20260130217</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>SK111100000639318227</t>
+          <t>20260206040</t>
         </is>
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="0">
-        <v>4279</v>
+        <v>118</v>
       </c>
       <c r="B66" s="1">
-        <v>46062</v>
+        <v>46074</v>
       </c>
       <c r="C66" s="2">
-        <v>169.33</v>
+        <v>341.01</v>
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>20260127015</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
+          <t>20260204226</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
           <t>SK7809000000000000000021</t>
         </is>
       </c>
-      <c r="F66" s="0" t="inlineStr">
+      <c r="G66" s="0" t="inlineStr">
         <is>
           <t>Jana Tvorivá - Creative Studio</t>
         </is>
@@ -2078,129 +2409,154 @@
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="0">
-        <v>4297</v>
+        <v>167</v>
       </c>
       <c r="B67" s="1">
-        <v>46063</v>
+        <v>46075</v>
       </c>
       <c r="C67" s="2">
-        <v>-417.63</v>
+        <v>789.74</v>
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>20260130024</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>2O260216251</t>
         </is>
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="0">
-        <v>4300</v>
+        <v>79</v>
       </c>
       <c r="B68" s="1">
-        <v>46063</v>
+        <v>46076</v>
       </c>
       <c r="C68" s="2">
-        <v>-1475.32</v>
+        <v>256.96</v>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>2O260202028</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260128020</t>
         </is>
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="0">
-        <v>4269</v>
+        <v>179</v>
       </c>
       <c r="B69" s="1">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="C69" s="2">
-        <v>209.82</v>
+        <v>-498.34</v>
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>20260121003</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260219260</t>
         </is>
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="0">
-        <v>4326</v>
+        <v>183</v>
       </c>
       <c r="B70" s="1">
-        <v>46064</v>
+        <v>46077</v>
       </c>
       <c r="C70" s="2">
-        <v>-175.46</v>
+        <v>347.68</v>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>2O260205036</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>2O260219066</t>
         </is>
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="0">
-        <v>4273</v>
+        <v>145</v>
       </c>
       <c r="B71" s="1">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="C71" s="2">
-        <v>268.55</v>
+        <v>256.21</v>
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>20260123011</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
+          <t>20260210237</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
           <t>SK481100000332819938</t>
         </is>
       </c>
-      <c r="F71" s="0" t="inlineStr">
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>Lucia Prekladová - LINGUA</t>
         </is>
@@ -2208,129 +2564,150 @@
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="0">
-        <v>4291</v>
+        <v>173</v>
       </c>
       <c r="B72" s="1">
-        <v>46064</v>
+        <v>46079</v>
       </c>
       <c r="C72" s="2">
-        <v>724.41</v>
+        <v>-1329.43</v>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>20260129214</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260217060</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="0">
-        <v>4336</v>
+        <v>80</v>
       </c>
       <c r="B73" s="1">
-        <v>46065</v>
+        <v>46079</v>
       </c>
       <c r="C73" s="2">
-        <v>-604.2</v>
+        <v>419.52</v>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>UHRADA38</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260128212</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="0">
-        <v>4339</v>
+        <v>188</v>
       </c>
       <c r="B74" s="1">
-        <v>46065</v>
+        <v>46081</v>
       </c>
       <c r="C74" s="2">
-        <v>750</v>
+        <v>674.46</v>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>UHRADA33</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260223073</t>
         </is>
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="0">
-        <v>4283</v>
+        <v>196</v>
       </c>
       <c r="B75" s="1">
-        <v>46066</v>
+        <v>46081</v>
       </c>
       <c r="C75" s="2">
-        <v>419.53</v>
+        <v>-7.5</v>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>20260128212</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
-        </is>
-      </c>
-      <c r="F75" s="0" t="inlineStr">
-        <is>
-          <t>Alza.cz a.s.</t>
+          <t>POPLATOK 02/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr"/>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>Mesačný poplatok za účet</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="0">
-        <v>4362</v>
+        <v>222</v>
       </c>
       <c r="B76" s="1">
-        <v>46066</v>
+        <v>46082</v>
       </c>
       <c r="C76" s="2">
-        <v>725.82</v>
+        <v>708.76</v>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>20260212053</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
+          <t>2O260224077</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
           <t>SK7809000000000000000021</t>
         </is>
       </c>
-      <c r="F76" s="0" t="inlineStr">
+      <c r="G76" s="0" t="inlineStr">
         <is>
           <t>Jana Tvorivá - Creative Studio</t>
         </is>
@@ -2338,103 +2715,123 @@
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="0">
-        <v>4356</v>
+        <v>219</v>
       </c>
       <c r="B77" s="1">
-        <v>46066</v>
+        <v>46082</v>
       </c>
       <c r="C77" s="2">
-        <v>187.22</v>
+        <v>409.37</v>
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>20260211241</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>UHRADA56</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="0">
-        <v>4314</v>
+        <v>231</v>
       </c>
       <c r="B78" s="1">
-        <v>46066</v>
+        <v>46083</v>
       </c>
       <c r="C78" s="2">
-        <v>1126.29</v>
+        <v>793.5</v>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>2O260204227</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>UHRADA30</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="0">
-        <v>4276</v>
+        <v>228</v>
       </c>
       <c r="B79" s="1">
-        <v>46067</v>
+        <v>46083</v>
       </c>
       <c r="C79" s="2">
-        <v>-592.73</v>
+        <v>778.26</v>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>20260126204</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>2O260225270</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="0">
-        <v>4359</v>
+        <v>223</v>
       </c>
       <c r="B80" s="1">
-        <v>46067</v>
+        <v>46083</v>
       </c>
       <c r="C80" s="2">
-        <v>-255.82</v>
+        <v>-183.55</v>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>20260211240</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
+          <t>20260225080</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
           <t>SK9509000000000000000006</t>
         </is>
       </c>
-      <c r="F80" s="0" t="inlineStr">
+      <c r="G80" s="0" t="inlineStr">
         <is>
           <t>KROS a.s.</t>
         </is>
@@ -2442,103 +2839,123 @@
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="0">
-        <v>4287</v>
+        <v>212</v>
       </c>
       <c r="B81" s="1">
-        <v>46067</v>
+        <v>46083</v>
       </c>
       <c r="C81" s="2">
-        <v>451.99</v>
+        <v>-498.35</v>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>20260129215</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>20260219260</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="0">
-        <v>4321</v>
+        <v>234</v>
       </c>
       <c r="B82" s="1">
-        <v>46068</v>
+        <v>46084</v>
       </c>
       <c r="C82" s="2">
-        <v>341.01</v>
+        <v>671.8</v>
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>20260204226</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>20260226274</t>
         </is>
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="0">
-        <v>4364</v>
+        <v>239</v>
       </c>
       <c r="B83" s="1">
-        <v>46069</v>
+        <v>46084</v>
       </c>
       <c r="C83" s="2">
-        <v>437.45</v>
+        <v>717.99</v>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>UHRADA88</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>UHRADA82</t>
         </is>
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="0">
-        <v>4346</v>
+        <v>237</v>
       </c>
       <c r="B84" s="1">
-        <v>46069</v>
+        <v>46085</v>
       </c>
       <c r="C84" s="2">
-        <v>1038.57</v>
+        <v>924.56</v>
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>20260209042</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
+          <t>UHRADA43</t>
+        </is>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
           <t>SK8009000000000000000010</t>
         </is>
       </c>
-      <c r="F84" s="0" t="inlineStr">
+      <c r="G84" s="0" t="inlineStr">
         <is>
           <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
@@ -2546,155 +2963,185 @@
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="0">
-        <v>4280</v>
+        <v>241</v>
       </c>
       <c r="B85" s="1">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="C85" s="2">
-        <v>533.79</v>
+        <v>1478.94</v>
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>20260127209</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260302279</t>
         </is>
       </c>
       <c r="F85" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="0">
-        <v>4349</v>
+        <v>240</v>
       </c>
       <c r="B86" s="1">
-        <v>46069</v>
+        <v>46087</v>
       </c>
       <c r="C86" s="2">
-        <v>3300</v>
+        <v>1570.94</v>
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>UHRADA70</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
+          <t>20260227085</t>
         </is>
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t>Alza.cz a.s.</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="0">
-        <v>4370</v>
+        <v>199</v>
       </c>
       <c r="B87" s="1">
-        <v>46070</v>
+        <v>46087</v>
       </c>
       <c r="C87" s="2">
-        <v>420.92</v>
+        <v>550</v>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>UHRADA77</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260037</t>
         </is>
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="0">
-        <v>4316</v>
+        <v>225</v>
       </c>
       <c r="B88" s="1">
-        <v>46073</v>
+        <v>46087</v>
       </c>
       <c r="C88" s="2">
-        <v>717.54</v>
+        <v>971.51</v>
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>20260204033</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260225271</t>
         </is>
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="0">
-        <v>4331</v>
+        <v>229</v>
       </c>
       <c r="B89" s="1">
-        <v>46073</v>
+        <v>46087</v>
       </c>
       <c r="C89" s="2">
-        <v>641.87</v>
+        <v>1085.74</v>
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>20260206231</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260225079</t>
         </is>
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="0">
-        <v>4383</v>
+        <v>224</v>
       </c>
       <c r="B90" s="1">
-        <v>46073</v>
+        <v>46088</v>
       </c>
       <c r="C90" s="2">
-        <v>-1170.44</v>
+        <v>-183.55</v>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>2O260217252</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
+          <t>20260225080</t>
+        </is>
+      </c>
+      <c r="F90" s="0" t="inlineStr">
+        <is>
           <t>SK9509000000000000000006</t>
         </is>
       </c>
-      <c r="F90" s="0" t="inlineStr">
+      <c r="G90" s="0" t="inlineStr">
         <is>
           <t>KROS a.s.</t>
         </is>
@@ -2702,25 +3149,30 @@
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="0">
-        <v>4333</v>
+        <v>263</v>
       </c>
       <c r="B91" s="1">
-        <v>46074</v>
+        <v>46089</v>
       </c>
       <c r="C91" s="2">
-        <v>490.94</v>
+        <v>729.64</v>
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>20260206041</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
+          <t>20260305098</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
           <t>SK7809000000000000000021</t>
         </is>
       </c>
-      <c r="F91" s="0" t="inlineStr">
+      <c r="G91" s="0" t="inlineStr">
         <is>
           <t>Jana Tvorivá - Creative Studio</t>
         </is>
@@ -2728,410 +3180,495 @@
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="0">
-        <v>4392</v>
+        <v>257</v>
       </c>
       <c r="B92" s="1">
-        <v>46074</v>
+        <v>46089</v>
       </c>
       <c r="C92" s="2">
-        <v>807.87</v>
+        <v>480.24</v>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>2O260219259</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>20260304094</t>
         </is>
       </c>
       <c r="F92" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="0">
-        <v>4335</v>
+        <v>235</v>
       </c>
       <c r="B93" s="1">
-        <v>46075</v>
+        <v>46091</v>
       </c>
       <c r="C93" s="2">
-        <v>900</v>
+        <v>671.8</v>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>20260041</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260226274</t>
         </is>
       </c>
       <c r="F93" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="0">
-        <v>4393</v>
+        <v>242</v>
       </c>
       <c r="B94" s="1">
-        <v>46075</v>
+        <v>46092</v>
       </c>
       <c r="C94" s="2">
-        <v>173.84</v>
+        <v>-1201.88</v>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>20260219066</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>2O260302280</t>
         </is>
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="0">
-        <v>4386</v>
+        <v>233</v>
       </c>
       <c r="B95" s="1">
-        <v>46076</v>
+        <v>46092</v>
       </c>
       <c r="C95" s="2">
-        <v>281.1</v>
+        <v>1218.07</v>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>2O260218257</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>20260226081</t>
         </is>
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="0">
-        <v>4374</v>
+        <v>203</v>
       </c>
       <c r="B96" s="1">
-        <v>46076</v>
+        <v>46093</v>
       </c>
       <c r="C96" s="2">
-        <v>658.97</v>
+        <v>234.88</v>
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>2O260216059</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260206233</t>
         </is>
       </c>
       <c r="F96" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="0">
-        <v>4388</v>
+        <v>217</v>
       </c>
       <c r="B97" s="1">
-        <v>46077</v>
+        <v>46093</v>
       </c>
       <c r="C97" s="2">
-        <v>1397.23</v>
+        <v>674.46</v>
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t>UHRADA55</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260223073</t>
         </is>
       </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="0">
-        <v>4398</v>
+        <v>201</v>
       </c>
       <c r="B98" s="1">
-        <v>46077</v>
+        <v>46094</v>
       </c>
       <c r="C98" s="2">
-        <v>465.89</v>
+        <v>419.53</v>
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>20260223074</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260128212</t>
         </is>
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="0">
-        <v>4394</v>
+        <v>267</v>
       </c>
       <c r="B99" s="1">
-        <v>46077</v>
+        <v>46094</v>
       </c>
       <c r="C99" s="2">
-        <v>1233.48</v>
+        <v>387.25</v>
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>2O260220070</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>UHRADA12</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="0">
-        <v>4400</v>
+        <v>200</v>
       </c>
       <c r="B100" s="1">
-        <v>46078</v>
+        <v>46094</v>
       </c>
       <c r="C100" s="2">
-        <v>-454.65</v>
+        <v>256.95</v>
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>20260223072</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260128020</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="0">
-        <v>4360</v>
+        <v>264</v>
       </c>
       <c r="B101" s="1">
-        <v>46078</v>
+        <v>46095</v>
       </c>
       <c r="C101" s="2">
-        <v>-255.82</v>
+        <v>729.63</v>
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>20260211240</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260305098</t>
         </is>
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="0">
-        <v>4377</v>
+        <v>271</v>
       </c>
       <c r="B102" s="1">
-        <v>46079</v>
+        <v>46097</v>
       </c>
       <c r="C102" s="2">
-        <v>337.65</v>
+        <v>1256.15</v>
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>2O260216250</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>UHRADA13</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="0">
-        <v>4402</v>
+        <v>198</v>
       </c>
       <c r="B103" s="1">
-        <v>46079</v>
+        <v>46097</v>
       </c>
       <c r="C103" s="2">
-        <v>710.44</v>
+        <v>750</v>
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>20260224269</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>1152026</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="0">
-        <v>4407</v>
+        <v>258</v>
       </c>
       <c r="B104" s="1">
-        <v>46081</v>
+        <v>46101</v>
       </c>
       <c r="C104" s="2">
-        <v>-7.5</v>
+        <v>480.25</v>
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>POPLATOK 02/2026</t>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>20260304094</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
         <is>
-          <t>Mesačný poplatok za účet</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="0">
-        <v>4404</v>
+        <v>304</v>
       </c>
       <c r="B105" s="1">
-        <v>46081</v>
+        <v>46106</v>
       </c>
       <c r="C105" s="2">
-        <v>-183.55</v>
+        <v>1028.32</v>
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>20260225080</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260323134</t>
         </is>
       </c>
       <c r="F105" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="0">
-        <v>4414</v>
+        <v>306</v>
       </c>
       <c r="B106" s="1">
-        <v>46082</v>
+        <v>46106</v>
       </c>
       <c r="C106" s="2">
-        <v>306.79</v>
+        <v>910.56</v>
       </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
-          <t>2O260219258</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>UHRADA42</t>
         </is>
       </c>
       <c r="F106" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="0">
-        <v>4442</v>
+        <v>302</v>
       </c>
       <c r="B107" s="1">
-        <v>46082</v>
+        <v>46106</v>
       </c>
       <c r="C107" s="2">
-        <v>785.47</v>
+        <v>544.16</v>
       </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
-          <t>20260227085</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
+          <t>20260323133</t>
+        </is>
+      </c>
+      <c r="F107" s="0" t="inlineStr">
+        <is>
           <t>SK3309000000000000000011</t>
         </is>
       </c>
-      <c r="F107" s="0" t="inlineStr">
+      <c r="G107" s="0" t="inlineStr">
         <is>
           <t>Flux a.s.</t>
         </is>
@@ -3139,103 +3676,119 @@
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="0">
-        <v>4432</v>
+        <v>309</v>
       </c>
       <c r="B108" s="1">
-        <v>46082</v>
+        <v>46109</v>
       </c>
       <c r="C108" s="2">
-        <v>396.75</v>
+        <v>345.12</v>
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>20260226275</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260326143</t>
         </is>
       </c>
       <c r="F108" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G108" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="0">
-        <v>4427</v>
+        <v>310</v>
       </c>
       <c r="B109" s="1">
-        <v>46083</v>
+        <v>46109</v>
       </c>
       <c r="C109" s="2">
-        <v>971.51</v>
+        <v>1182.46</v>
       </c>
       <c r="D109" s="0" t="inlineStr">
         <is>
-          <t>UHRADA16</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>UHRADA44</t>
         </is>
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G109" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="0">
-        <v>4422</v>
+        <v>311</v>
       </c>
       <c r="B110" s="1">
-        <v>46083</v>
+        <v>46109</v>
       </c>
       <c r="C110" s="2">
-        <v>166.55</v>
+        <v>-7.5</v>
       </c>
       <c r="D110" s="0" t="inlineStr">
         <is>
-          <t>UHRADA70</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
-        </is>
-      </c>
-      <c r="F110" s="0" t="inlineStr">
-        <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>POPLATOK 03/2026</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="inlineStr"/>
+      <c r="G110" s="0" t="inlineStr">
+        <is>
+          <t>Mesačný poplatok za účet</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="0">
-        <v>4439</v>
+        <v>307</v>
       </c>
       <c r="B111" s="1">
-        <v>46083</v>
+        <v>46110</v>
       </c>
       <c r="C111" s="2">
-        <v>389.76</v>
+        <v>761.98</v>
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
-          <t>UHRADA24</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
+          <t>2O260325139</t>
+        </is>
+      </c>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
           <t>SK8009000000000000000010</t>
         </is>
       </c>
-      <c r="F111" s="0" t="inlineStr">
+      <c r="G111" s="0" t="inlineStr">
         <is>
           <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
@@ -3243,181 +3796,216 @@
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="0">
-        <v>4413</v>
+        <v>327</v>
       </c>
       <c r="B112" s="1">
-        <v>46084</v>
+        <v>46113</v>
       </c>
       <c r="C112" s="2">
-        <v>173.84</v>
+        <v>1061.44</v>
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>20260219066</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>UHRADA71</t>
         </is>
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="0">
-        <v>4418</v>
+        <v>326</v>
       </c>
       <c r="B113" s="1">
-        <v>46084</v>
+        <v>46114</v>
       </c>
       <c r="C113" s="2">
-        <v>-454.65</v>
+        <v>1334.97</v>
       </c>
       <c r="D113" s="0" t="inlineStr">
         <is>
-          <t>20260223072</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>UHRADA61</t>
         </is>
       </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="0">
-        <v>4408</v>
+        <v>321</v>
       </c>
       <c r="B114" s="1">
-        <v>46084</v>
+        <v>46114</v>
       </c>
       <c r="C114" s="2">
-        <v>187.22</v>
+        <v>717.54</v>
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>20260211241</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
+          <t>UHRADA81</t>
         </is>
       </c>
       <c r="F114" s="0" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>SK8009000000000000000010</t>
+        </is>
+      </c>
+      <c r="G114" s="0" t="inlineStr">
+        <is>
+          <t>Ing. Pavol Vnuk - NORPAL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="0">
-        <v>4449</v>
+        <v>335</v>
       </c>
       <c r="B115" s="1">
-        <v>46085</v>
+        <v>46116</v>
       </c>
       <c r="C115" s="2">
-        <v>447.08</v>
+        <v>850</v>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>20260302281</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>2O260051</t>
         </is>
       </c>
       <c r="F115" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G115" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="0">
-        <v>4435</v>
+        <v>333</v>
       </c>
       <c r="B116" s="1">
-        <v>46085</v>
+        <v>46116</v>
       </c>
       <c r="C116" s="2">
-        <v>1218.07</v>
+        <v>200</v>
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>20260226081</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
-          <t>SK931100000844214855</t>
+          <t>20260050</t>
         </is>
       </c>
       <c r="F116" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G116" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="0">
-        <v>4425</v>
+        <v>320</v>
       </c>
       <c r="B117" s="1">
-        <v>46085</v>
+        <v>46116</v>
       </c>
       <c r="C117" s="2">
-        <v>564.58</v>
+        <v>112.32</v>
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>2O260224075</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>2O260327144</t>
         </is>
       </c>
       <c r="F117" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>CZ2601000000000000000019</t>
+        </is>
+      </c>
+      <c r="G117" s="0" t="inlineStr">
+        <is>
+          <t>Alza.cz a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="0">
-        <v>4409</v>
+        <v>323</v>
       </c>
       <c r="B118" s="1">
-        <v>46085</v>
+        <v>46117</v>
       </c>
       <c r="C118" s="2">
-        <v>725.82</v>
+        <v>462.29</v>
       </c>
       <c r="D118" s="0" t="inlineStr">
         <is>
-          <t>20260212053</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
+          <t>20260330147</t>
+        </is>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
           <t>SK7809000000000000000021</t>
         </is>
       </c>
-      <c r="F118" s="0" t="inlineStr">
+      <c r="G118" s="0" t="inlineStr">
         <is>
           <t>Jana Tvorivá - Creative Studio</t>
         </is>
@@ -3425,259 +4013,309 @@
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="0">
-        <v>4417</v>
+        <v>318</v>
       </c>
       <c r="B119" s="1">
-        <v>46086</v>
+        <v>46120</v>
       </c>
       <c r="C119" s="2">
-        <v>465.89</v>
+        <v>345.12</v>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>20260223074</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260326143</t>
         </is>
       </c>
       <c r="F119" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G119" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="0">
-        <v>4460</v>
+        <v>315</v>
       </c>
       <c r="B120" s="1">
-        <v>46087</v>
+        <v>46120</v>
       </c>
       <c r="C120" s="2">
-        <v>1378.37</v>
+        <v>544.16</v>
       </c>
       <c r="D120" s="0" t="inlineStr">
         <is>
-          <t>UHRADA25</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
+          <t>20260323133</t>
         </is>
       </c>
       <c r="F120" s="0" t="inlineStr">
         <is>
-          <t>Alza.cz a.s.</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G120" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="0">
-        <v>4421</v>
+        <v>330</v>
       </c>
       <c r="B121" s="1">
-        <v>46087</v>
+        <v>46120</v>
       </c>
       <c r="C121" s="2">
-        <v>1493.61</v>
+        <v>814.44</v>
       </c>
       <c r="D121" s="0" t="inlineStr">
         <is>
-          <t>2O260224076</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
-          <t>CZ2601000000000000000019</t>
+          <t>2O260401155</t>
         </is>
       </c>
       <c r="F121" s="0" t="inlineStr">
         <is>
-          <t>Alza.cz a.s.</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G121" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="0">
-        <v>4452</v>
+        <v>336</v>
       </c>
       <c r="B122" s="1">
-        <v>46087</v>
+        <v>46120</v>
       </c>
       <c r="C122" s="2">
-        <v>-631.66</v>
+        <v>589.02</v>
       </c>
       <c r="D122" s="0" t="inlineStr">
         <is>
-          <t>20260303284</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260402157</t>
         </is>
       </c>
       <c r="F122" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="0">
-        <v>4429</v>
+        <v>338</v>
       </c>
       <c r="B123" s="1">
-        <v>46087</v>
+        <v>46121</v>
       </c>
       <c r="C123" s="2">
-        <v>580.01</v>
+        <v>590.53</v>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>2O260225078</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>2O260402158</t>
         </is>
       </c>
       <c r="F123" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="0">
-        <v>4451</v>
+        <v>346</v>
       </c>
       <c r="B124" s="1">
-        <v>46088</v>
+        <v>46121</v>
       </c>
       <c r="C124" s="2">
-        <v>-120</v>
+        <v>498.71</v>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>3367O4</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260407165</t>
         </is>
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G124" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="0">
-        <v>4433</v>
+        <v>344</v>
       </c>
       <c r="B125" s="1">
-        <v>46089</v>
+        <v>46121</v>
       </c>
       <c r="C125" s="2">
-        <v>396.75</v>
+        <v>457.68</v>
       </c>
       <c r="D125" s="0" t="inlineStr">
         <is>
-          <t>20260226275</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260406162</t>
         </is>
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G125" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="0">
-        <v>4456</v>
+        <v>312</v>
       </c>
       <c r="B126" s="1">
-        <v>46090</v>
+        <v>46121</v>
       </c>
       <c r="C126" s="2">
-        <v>548</v>
+        <v>234.89</v>
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
-          <t>2O260303282</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>20260206233</t>
         </is>
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G126" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="0">
-        <v>4447</v>
+        <v>351</v>
       </c>
       <c r="B127" s="1">
-        <v>46090</v>
+        <v>46123</v>
       </c>
       <c r="C127" s="2">
-        <v>203.64</v>
+        <v>1064.3</v>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>UHRADA41</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>UHRADA15</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="0">
-        <v>4443</v>
+        <v>337</v>
       </c>
       <c r="B128" s="1">
-        <v>46090</v>
+        <v>46127</v>
       </c>
       <c r="C128" s="2">
-        <v>785.47</v>
+        <v>589.01</v>
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>20260227085</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
+          <t>20260402157</t>
+        </is>
+      </c>
+      <c r="F128" s="0" t="inlineStr">
+        <is>
           <t>SK3309000000000000000011</t>
         </is>
       </c>
-      <c r="F128" s="0" t="inlineStr">
+      <c r="G128" s="0" t="inlineStr">
         <is>
           <t>Flux a.s.</t>
         </is>
@@ -3685,129 +4323,154 @@
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="0">
-        <v>4473</v>
+        <v>324</v>
       </c>
       <c r="B129" s="1">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C129" s="2">
-        <v>-774.93</v>
+        <v>462.29</v>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>20260309104</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
-          <t>SK9509000000000000000006</t>
+          <t>20260330147</t>
         </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
-          <t>KROS a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G129" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="0">
-        <v>4459</v>
+        <v>361</v>
       </c>
       <c r="B130" s="1">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C130" s="2">
-        <v>400</v>
+        <v>662.23</v>
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>UHRADA81</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
-          <t>SK7809000000000000000021</t>
+          <t>2O260414182</t>
         </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t>Jana Tvorivá - Creative Studio</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G130" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="0">
-        <v>4480</v>
+        <v>334</v>
       </c>
       <c r="B131" s="1">
-        <v>46092</v>
+        <v>46128</v>
       </c>
       <c r="C131" s="2">
-        <v>498.18</v>
+        <v>200</v>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>20260310106</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
-          <t>SK3309000000000000000011</t>
+          <t>20260050</t>
         </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t>Flux a.s.</t>
+          <t>SK7809000000000000000021</t>
+        </is>
+      </c>
+      <c r="G131" s="0" t="inlineStr">
+        <is>
+          <t>Jana Tvorivá - Creative Studio</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="0">
-        <v>4444</v>
+        <v>357</v>
       </c>
       <c r="B132" s="1">
-        <v>46092</v>
+        <v>46129</v>
       </c>
       <c r="C132" s="2">
-        <v>1478.94</v>
+        <v>1009.46</v>
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>20260302279</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>2O260410174</t>
         </is>
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>GB46BARC00000000000020</t>
+        </is>
+      </c>
+      <c r="G132" s="0" t="inlineStr">
+        <is>
+          <t>British Airways</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="0">
-        <v>4478</v>
+        <v>355</v>
       </c>
       <c r="B133" s="1">
-        <v>46093</v>
+        <v>46130</v>
       </c>
       <c r="C133" s="2">
-        <v>550</v>
+        <v>361.9</v>
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
-          <t>UHRADA71</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
+          <t>2O260409171</t>
+        </is>
+      </c>
+      <c r="F133" s="0" t="inlineStr">
+        <is>
           <t>SK481100000332819938</t>
         </is>
       </c>
-      <c r="F133" s="0" t="inlineStr">
+      <c r="G133" s="0" t="inlineStr">
         <is>
           <t>Lucia Prekladová - LINGUA</t>
         </is>
@@ -3815,51 +4478,61 @@
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="0">
-        <v>4485</v>
+        <v>366</v>
       </c>
       <c r="B134" s="1">
-        <v>46094</v>
+        <v>46130</v>
       </c>
       <c r="C134" s="2">
-        <v>643.83</v>
+        <v>-45.9</v>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>20260311109</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>3163591O</t>
         </is>
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK9509000000000000000006</t>
+        </is>
+      </c>
+      <c r="G134" s="0" t="inlineStr">
+        <is>
+          <t>KROS a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="0">
-        <v>4487</v>
+        <v>363</v>
       </c>
       <c r="B135" s="1">
-        <v>46094</v>
+        <v>46131</v>
       </c>
       <c r="C135" s="2">
-        <v>411.88</v>
+        <v>1100</v>
       </c>
       <c r="D135" s="0" t="inlineStr">
         <is>
-          <t>20260312113</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
+          <t>2O260056</t>
+        </is>
+      </c>
+      <c r="F135" s="0" t="inlineStr">
+        <is>
           <t>GB46BARC00000000000020</t>
         </is>
       </c>
-      <c r="F135" s="0" t="inlineStr">
+      <c r="G135" s="0" t="inlineStr">
         <is>
           <t>British Airways</t>
         </is>
@@ -3867,77 +4540,88 @@
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="0">
-        <v>4457</v>
+        <v>367</v>
       </c>
       <c r="B136" s="1">
-        <v>46094</v>
+        <v>46133</v>
       </c>
       <c r="C136" s="2">
-        <v>1500</v>
+        <v>-7.5</v>
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>2O260045</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F136" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
+          <t>POPLATOK 04/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="0" t="inlineStr"/>
+      <c r="G136" s="0" t="inlineStr">
+        <is>
+          <t>Mesačný poplatok za účet</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="0">
-        <v>4423</v>
+        <v>347</v>
       </c>
       <c r="B137" s="1">
-        <v>46095</v>
+        <v>46133</v>
       </c>
       <c r="C137" s="2">
-        <v>710.45</v>
+        <v>498.71</v>
       </c>
       <c r="D137" s="0" t="inlineStr">
         <is>
-          <t>20260224269</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E137" s="0" t="inlineStr">
         <is>
-          <t>SK481100000332819938</t>
+          <t>20260407165</t>
         </is>
       </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
-          <t>Lucia Prekladová - LINGUA</t>
+          <t>SK3309000000000000000011</t>
+        </is>
+      </c>
+      <c r="G137" s="0" t="inlineStr">
+        <is>
+          <t>Flux a.s.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="0">
-        <v>4475</v>
+        <v>364</v>
       </c>
       <c r="B138" s="1">
-        <v>46096</v>
+        <v>46133</v>
       </c>
       <c r="C138" s="2">
-        <v>1027.38</v>
+        <v>323.49</v>
       </c>
       <c r="D138" s="0" t="inlineStr">
         <is>
-          <t>UHRADA83</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E138" s="0" t="inlineStr">
         <is>
+          <t>2O260417191</t>
+        </is>
+      </c>
+      <c r="F138" s="0" t="inlineStr">
+        <is>
           <t>GB46BARC00000000000020</t>
         </is>
       </c>
-      <c r="F138" s="0" t="inlineStr">
+      <c r="G138" s="0" t="inlineStr">
         <is>
           <t>British Airways</t>
         </is>
@@ -3945,1163 +4629,384 @@
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="0">
-        <v>4450</v>
+        <v>345</v>
       </c>
       <c r="B139" s="1">
-        <v>46096</v>
+        <v>46133</v>
       </c>
       <c r="C139" s="2">
-        <v>447.09</v>
+        <v>457.69</v>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>20260302281</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E139" s="0" t="inlineStr">
         <is>
-          <t>SK8009000000000000000010</t>
+          <t>20260406162</t>
         </is>
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
+          <t>SK481100000332819938</t>
+        </is>
+      </c>
+      <c r="G139" s="0" t="inlineStr">
+        <is>
+          <t>Lucia Prekladová - LINGUA</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="140">
-      <c r="A140" s="0">
-        <v>4426</v>
-      </c>
-      <c r="B140" s="1">
-        <v>46096</v>
-      </c>
-      <c r="C140" s="2">
-        <v>-183.55</v>
-      </c>
-      <c r="D140" s="0" t="inlineStr">
-        <is>
-          <t>20260225080</t>
-        </is>
-      </c>
-      <c r="E140" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F140" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A140" s="0"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="0" t="inlineStr"/>
+      <c r="E140" s="0" t="inlineStr"/>
+      <c r="F140" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="141">
-      <c r="A141" s="0">
-        <v>4492</v>
-      </c>
-      <c r="B141" s="1">
-        <v>46096</v>
-      </c>
-      <c r="C141" s="2">
-        <v>1346.64</v>
-      </c>
-      <c r="D141" s="0" t="inlineStr">
-        <is>
-          <t>UHRADA9</t>
-        </is>
-      </c>
-      <c r="E141" s="0" t="inlineStr">
-        <is>
-          <t>CZ2601000000000000000019</t>
-        </is>
-      </c>
-      <c r="F141" s="0" t="inlineStr">
-        <is>
-          <t>Alza.cz a.s.</t>
-        </is>
-      </c>
+      <c r="A141" s="0"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="0" t="inlineStr"/>
+      <c r="E141" s="0" t="inlineStr"/>
+      <c r="F141" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="142">
-      <c r="A142" s="0">
-        <v>4474</v>
-      </c>
-      <c r="B142" s="1">
-        <v>46097</v>
-      </c>
-      <c r="C142" s="2">
-        <v>-774.93</v>
-      </c>
-      <c r="D142" s="0" t="inlineStr">
-        <is>
-          <t>20260309104</t>
-        </is>
-      </c>
-      <c r="E142" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F142" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A142" s="0"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="0" t="inlineStr"/>
+      <c r="E142" s="0" t="inlineStr"/>
+      <c r="F142" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="143">
-      <c r="A143" s="0">
-        <v>4496</v>
-      </c>
-      <c r="B143" s="1">
-        <v>46098</v>
-      </c>
-      <c r="C143" s="2">
-        <v>-22.95</v>
-      </c>
-      <c r="D143" s="0" t="inlineStr">
-        <is>
-          <t>31635909</t>
-        </is>
-      </c>
-      <c r="E143" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F143" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A143" s="0"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="0" t="inlineStr"/>
+      <c r="E143" s="0" t="inlineStr"/>
+      <c r="F143" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="144">
-      <c r="A144" s="0">
-        <v>4453</v>
-      </c>
-      <c r="B144" s="1">
-        <v>46099</v>
-      </c>
-      <c r="C144" s="2">
-        <v>-631.67</v>
-      </c>
-      <c r="D144" s="0" t="inlineStr">
-        <is>
-          <t>20260303284</t>
-        </is>
-      </c>
-      <c r="E144" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F144" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A144" s="0"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="0" t="inlineStr"/>
+      <c r="E144" s="0" t="inlineStr"/>
+      <c r="F144" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="145">
-      <c r="A145" s="0">
-        <v>4486</v>
-      </c>
-      <c r="B145" s="1">
-        <v>46101</v>
-      </c>
-      <c r="C145" s="2">
-        <v>643.82</v>
-      </c>
-      <c r="D145" s="0" t="inlineStr">
-        <is>
-          <t>20260311109</t>
-        </is>
-      </c>
-      <c r="E145" s="0" t="inlineStr">
-        <is>
-          <t>SK481100000332819938</t>
-        </is>
-      </c>
-      <c r="F145" s="0" t="inlineStr">
-        <is>
-          <t>Lucia Prekladová - LINGUA</t>
-        </is>
-      </c>
+      <c r="A145" s="0"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="0" t="inlineStr"/>
+      <c r="E145" s="0" t="inlineStr"/>
+      <c r="F145" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="146">
-      <c r="A146" s="0">
-        <v>4489</v>
-      </c>
-      <c r="B146" s="1">
-        <v>46101</v>
-      </c>
-      <c r="C146" s="2">
-        <v>1337.61</v>
-      </c>
-      <c r="D146" s="0" t="inlineStr">
-        <is>
-          <t>2O260312112</t>
-        </is>
-      </c>
-      <c r="E146" s="0" t="inlineStr">
-        <is>
-          <t>CZ2601000000000000000019</t>
-        </is>
-      </c>
-      <c r="F146" s="0" t="inlineStr">
-        <is>
-          <t>Alza.cz a.s.</t>
-        </is>
-      </c>
+      <c r="A146" s="0"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="0" t="inlineStr"/>
+      <c r="E146" s="0" t="inlineStr"/>
+      <c r="F146" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="147">
-      <c r="A147" s="0">
-        <v>4504</v>
-      </c>
-      <c r="B147" s="1">
-        <v>46102</v>
-      </c>
-      <c r="C147" s="2">
-        <v>554.82</v>
-      </c>
-      <c r="D147" s="0" t="inlineStr">
-        <is>
-          <t>20260318125</t>
-        </is>
-      </c>
-      <c r="E147" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F147" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A147" s="0"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="0" t="inlineStr"/>
+      <c r="E147" s="0" t="inlineStr"/>
+      <c r="F147" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="148">
-      <c r="A148" s="0">
-        <v>4499</v>
-      </c>
-      <c r="B148" s="1">
-        <v>46104</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1039.83</v>
-      </c>
-      <c r="D148" s="0" t="inlineStr">
-        <is>
-          <t>UHRADA75</t>
-        </is>
-      </c>
-      <c r="E148" s="0" t="inlineStr">
-        <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F148" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
-        </is>
-      </c>
+      <c r="A148" s="0"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="0" t="inlineStr"/>
+      <c r="E148" s="0" t="inlineStr"/>
+      <c r="F148" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="149">
-      <c r="A149" s="0">
-        <v>4497</v>
-      </c>
-      <c r="B149" s="1">
-        <v>46107</v>
-      </c>
-      <c r="C149" s="2">
-        <v>-22.95</v>
-      </c>
-      <c r="D149" s="0" t="inlineStr">
-        <is>
-          <t>31635909</t>
-        </is>
-      </c>
-      <c r="E149" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F149" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A149" s="0"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="0" t="inlineStr"/>
+      <c r="E149" s="0" t="inlineStr"/>
+      <c r="F149" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="150">
-      <c r="A150" s="0">
-        <v>4513</v>
-      </c>
-      <c r="B150" s="1">
-        <v>46107</v>
-      </c>
-      <c r="C150" s="2">
-        <v>1015.13</v>
-      </c>
-      <c r="D150" s="0" t="inlineStr">
-        <is>
-          <t>2O260324137</t>
-        </is>
-      </c>
-      <c r="E150" s="0" t="inlineStr">
-        <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F150" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
-        </is>
-      </c>
+      <c r="A150" s="0"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="0" t="inlineStr"/>
+      <c r="E150" s="0" t="inlineStr"/>
+      <c r="F150" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="151">
-      <c r="A151" s="0">
-        <v>4481</v>
-      </c>
-      <c r="B151" s="1">
-        <v>46108</v>
-      </c>
-      <c r="C151" s="2">
-        <v>498.19</v>
-      </c>
-      <c r="D151" s="0" t="inlineStr">
-        <is>
-          <t>20260310106</t>
-        </is>
-      </c>
-      <c r="E151" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F151" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A151" s="0"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="0" t="inlineStr"/>
+      <c r="E151" s="0" t="inlineStr"/>
+      <c r="F151" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="152">
-      <c r="A152" s="0">
-        <v>4520</v>
-      </c>
-      <c r="B152" s="1">
-        <v>46109</v>
-      </c>
-      <c r="C152" s="2">
-        <v>717.54</v>
-      </c>
-      <c r="D152" s="0" t="inlineStr">
-        <is>
-          <t>UHRADA50</t>
-        </is>
-      </c>
-      <c r="E152" s="0" t="inlineStr">
-        <is>
-          <t>SK8009000000000000000010</t>
-        </is>
-      </c>
-      <c r="F152" s="0" t="inlineStr">
-        <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
-        </is>
-      </c>
+      <c r="A152" s="0"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="0" t="inlineStr"/>
+      <c r="E152" s="0" t="inlineStr"/>
+      <c r="F152" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="153">
-      <c r="A153" s="0">
-        <v>4521</v>
-      </c>
-      <c r="B153" s="1">
-        <v>46109</v>
-      </c>
-      <c r="C153" s="2">
-        <v>-7.5</v>
-      </c>
-      <c r="D153" s="0" t="inlineStr">
-        <is>
-          <t>POPLATOK 03/2026</t>
-        </is>
-      </c>
-      <c r="F153" s="0" t="inlineStr">
-        <is>
-          <t>Mesačný poplatok za účet</t>
-        </is>
-      </c>
+      <c r="A153" s="0"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="0" t="inlineStr"/>
+      <c r="F153" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="154">
-      <c r="A154" s="0">
-        <v>4516</v>
-      </c>
-      <c r="B154" s="1">
-        <v>46110</v>
-      </c>
-      <c r="C154" s="2">
-        <v>273.05</v>
-      </c>
-      <c r="D154" s="0" t="inlineStr">
-        <is>
-          <t>2O260326142</t>
-        </is>
-      </c>
-      <c r="E154" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F154" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A154" s="0"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="0" t="inlineStr"/>
+      <c r="E154" s="0" t="inlineStr"/>
+      <c r="F154" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="155">
-      <c r="A155" s="0">
-        <v>4507</v>
-      </c>
-      <c r="B155" s="1">
-        <v>46110</v>
-      </c>
-      <c r="C155" s="2">
-        <v>357.17</v>
-      </c>
-      <c r="D155" s="0" t="inlineStr">
-        <is>
-          <t>2O260319127</t>
-        </is>
-      </c>
-      <c r="E155" s="0" t="inlineStr">
-        <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F155" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
-        </is>
-      </c>
+      <c r="A155" s="0"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="0" t="inlineStr"/>
+      <c r="E155" s="0" t="inlineStr"/>
+      <c r="F155" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="156">
-      <c r="A156" s="0">
-        <v>4517</v>
-      </c>
-      <c r="B156" s="1">
-        <v>46111</v>
-      </c>
-      <c r="C156" s="2">
-        <v>1182.46</v>
-      </c>
-      <c r="D156" s="0" t="inlineStr">
-        <is>
-          <t>2O260326141</t>
-        </is>
-      </c>
-      <c r="E156" s="0" t="inlineStr">
-        <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F156" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
-        </is>
-      </c>
+      <c r="A156" s="0"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="0" t="inlineStr"/>
+      <c r="E156" s="0" t="inlineStr"/>
+      <c r="F156" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="157">
-      <c r="A157" s="0">
-        <v>4519</v>
-      </c>
-      <c r="B157" s="1">
-        <v>46112</v>
-      </c>
-      <c r="C157" s="2">
-        <v>112.32</v>
-      </c>
-      <c r="D157" s="0" t="inlineStr">
-        <is>
-          <t>2O260327144</t>
-        </is>
-      </c>
-      <c r="E157" s="0" t="inlineStr">
-        <is>
-          <t>CZ2601000000000000000019</t>
-        </is>
-      </c>
-      <c r="F157" s="0" t="inlineStr">
-        <is>
-          <t>Alza.cz a.s.</t>
-        </is>
-      </c>
+      <c r="A157" s="0"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="0" t="inlineStr"/>
+      <c r="E157" s="0" t="inlineStr"/>
+      <c r="F157" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="158">
-      <c r="A158" s="0">
-        <v>4488</v>
-      </c>
-      <c r="B158" s="1">
-        <v>46112</v>
-      </c>
-      <c r="C158" s="2">
-        <v>411.88</v>
-      </c>
-      <c r="D158" s="0" t="inlineStr">
-        <is>
-          <t>20260312113</t>
-        </is>
-      </c>
-      <c r="E158" s="0" t="inlineStr">
-        <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F158" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
-        </is>
-      </c>
+      <c r="A158" s="0"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="0" t="inlineStr"/>
+      <c r="E158" s="0" t="inlineStr"/>
+      <c r="F158" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="159">
-      <c r="A159" s="0">
-        <v>4524</v>
-      </c>
-      <c r="B159" s="1">
-        <v>46113</v>
-      </c>
-      <c r="C159" s="2">
-        <v>1088.32</v>
-      </c>
-      <c r="D159" s="0" t="inlineStr">
-        <is>
-          <t>20260323133</t>
-        </is>
-      </c>
-      <c r="E159" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F159" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A159" s="0"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="0" t="inlineStr"/>
+      <c r="E159" s="0" t="inlineStr"/>
+      <c r="F159" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="160">
-      <c r="A160" s="0">
-        <v>4529</v>
-      </c>
-      <c r="B160" s="1">
-        <v>46113</v>
-      </c>
-      <c r="C160" s="2">
-        <v>690.24</v>
-      </c>
-      <c r="D160" s="0" t="inlineStr">
-        <is>
-          <t>2O260326143</t>
-        </is>
-      </c>
-      <c r="E160" s="0" t="inlineStr">
-        <is>
-          <t>SK481100000332819938</t>
-        </is>
-      </c>
-      <c r="F160" s="0" t="inlineStr">
-        <is>
-          <t>Lucia Prekladová - LINGUA</t>
-        </is>
-      </c>
+      <c r="A160" s="0"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="0" t="inlineStr"/>
+      <c r="E160" s="0" t="inlineStr"/>
+      <c r="F160" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="161">
-      <c r="A161" s="0">
-        <v>4533</v>
-      </c>
-      <c r="B161" s="1">
-        <v>46113</v>
-      </c>
-      <c r="C161" s="2">
-        <v>-663.18</v>
-      </c>
-      <c r="D161" s="0" t="inlineStr">
-        <is>
-          <t>20260330148</t>
-        </is>
-      </c>
-      <c r="E161" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F161" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A161" s="0"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="0" t="inlineStr"/>
+      <c r="E161" s="0" t="inlineStr"/>
+      <c r="F161" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="162">
-      <c r="A162" s="0">
-        <v>4531</v>
-      </c>
-      <c r="B162" s="1">
-        <v>46114</v>
-      </c>
-      <c r="C162" s="2">
-        <v>462.29</v>
-      </c>
-      <c r="D162" s="0" t="inlineStr">
-        <is>
-          <t>20260330147</t>
-        </is>
-      </c>
-      <c r="E162" s="0" t="inlineStr">
-        <is>
-          <t>SK7809000000000000000021</t>
-        </is>
-      </c>
-      <c r="F162" s="0" t="inlineStr">
-        <is>
-          <t>Jana Tvorivá - Creative Studio</t>
-        </is>
-      </c>
+      <c r="A162" s="0"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="0" t="inlineStr"/>
+      <c r="E162" s="0" t="inlineStr"/>
+      <c r="F162" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="163">
-      <c r="A163" s="0">
-        <v>4546</v>
-      </c>
-      <c r="B163" s="1">
-        <v>46116</v>
-      </c>
-      <c r="C163" s="2">
-        <v>295.26</v>
-      </c>
-      <c r="D163" s="0" t="inlineStr">
-        <is>
-          <t>20260402158</t>
-        </is>
-      </c>
-      <c r="E163" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F163" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A163" s="0"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="0" t="inlineStr"/>
+      <c r="E163" s="0" t="inlineStr"/>
+      <c r="F163" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="164">
-      <c r="A164" s="0">
-        <v>4536</v>
-      </c>
-      <c r="B164" s="1">
-        <v>46116</v>
-      </c>
-      <c r="C164" s="2">
-        <v>1061.44</v>
-      </c>
-      <c r="D164" s="0" t="inlineStr">
-        <is>
-          <t>20260331151</t>
-        </is>
-      </c>
-      <c r="E164" s="0" t="inlineStr">
-        <is>
-          <t>SK7809000000000000000021</t>
-        </is>
-      </c>
-      <c r="F164" s="0" t="inlineStr">
-        <is>
-          <t>Jana Tvorivá - Creative Studio</t>
-        </is>
-      </c>
+      <c r="A164" s="0"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="0" t="inlineStr"/>
+      <c r="E164" s="0" t="inlineStr"/>
+      <c r="F164" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="165">
-      <c r="A165" s="0">
-        <v>4538</v>
-      </c>
-      <c r="B165" s="1">
-        <v>46116</v>
-      </c>
-      <c r="C165" s="2">
-        <v>553.82</v>
-      </c>
-      <c r="D165" s="0" t="inlineStr">
-        <is>
-          <t>20260401153</t>
-        </is>
-      </c>
-      <c r="E165" s="0" t="inlineStr">
-        <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F165" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
-        </is>
-      </c>
+      <c r="A165" s="0"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="0" t="inlineStr"/>
+      <c r="E165" s="0" t="inlineStr"/>
+      <c r="F165" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="166">
-      <c r="A166" s="0">
-        <v>4525</v>
-      </c>
-      <c r="B166" s="1">
-        <v>46116</v>
-      </c>
-      <c r="C166" s="2">
-        <v>1028.32</v>
-      </c>
-      <c r="D166" s="0" t="inlineStr">
-        <is>
-          <t>20260323134</t>
-        </is>
-      </c>
-      <c r="E166" s="0" t="inlineStr">
-        <is>
-          <t>SK8009000000000000000010</t>
-        </is>
-      </c>
-      <c r="F166" s="0" t="inlineStr">
-        <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
-        </is>
-      </c>
+      <c r="A166" s="0"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="0" t="inlineStr"/>
+      <c r="E166" s="0" t="inlineStr"/>
+      <c r="F166" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="167">
-      <c r="A167" s="0">
-        <v>4548</v>
-      </c>
-      <c r="B167" s="1">
-        <v>46117</v>
-      </c>
-      <c r="C167" s="2">
-        <v>600</v>
-      </c>
-      <c r="D167" s="0" t="inlineStr">
-        <is>
-          <t>20260049</t>
-        </is>
-      </c>
-      <c r="E167" s="0" t="inlineStr">
-        <is>
-          <t>SK8009000000000000000010</t>
-        </is>
-      </c>
-      <c r="F167" s="0" t="inlineStr">
-        <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
-        </is>
-      </c>
+      <c r="A167" s="0"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="0" t="inlineStr"/>
+      <c r="E167" s="0" t="inlineStr"/>
+      <c r="F167" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="168">
-      <c r="A168" s="0">
-        <v>4522</v>
-      </c>
-      <c r="B168" s="1">
-        <v>46118</v>
-      </c>
-      <c r="C168" s="2">
-        <v>554.81</v>
-      </c>
-      <c r="D168" s="0" t="inlineStr">
-        <is>
-          <t>20260318125</t>
-        </is>
-      </c>
-      <c r="E168" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F168" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A168" s="0"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="0" t="inlineStr"/>
+      <c r="E168" s="0" t="inlineStr"/>
+      <c r="F168" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="169">
-      <c r="A169" s="0">
-        <v>4532</v>
-      </c>
-      <c r="B169" s="1">
-        <v>46121</v>
-      </c>
-      <c r="C169" s="2">
-        <v>462.29</v>
-      </c>
-      <c r="D169" s="0" t="inlineStr">
-        <is>
-          <t>20260330147</t>
-        </is>
-      </c>
-      <c r="E169" s="0" t="inlineStr">
-        <is>
-          <t>SK7809000000000000000021</t>
-        </is>
-      </c>
-      <c r="F169" s="0" t="inlineStr">
-        <is>
-          <t>Jana Tvorivá - Creative Studio</t>
-        </is>
-      </c>
+      <c r="A169" s="0"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="0" t="inlineStr"/>
+      <c r="E169" s="0" t="inlineStr"/>
+      <c r="F169" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="170">
-      <c r="A170" s="0">
-        <v>4564</v>
-      </c>
-      <c r="B170" s="1">
-        <v>46122</v>
-      </c>
-      <c r="C170" s="2">
-        <v>768.19</v>
-      </c>
-      <c r="D170" s="0" t="inlineStr">
-        <is>
-          <t>2O260409173</t>
-        </is>
-      </c>
-      <c r="E170" s="0" t="inlineStr">
-        <is>
-          <t>SK481100000332819938</t>
-        </is>
-      </c>
-      <c r="F170" s="0" t="inlineStr">
-        <is>
-          <t>Lucia Prekladová - LINGUA</t>
-        </is>
-      </c>
+      <c r="A170" s="0"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="0" t="inlineStr"/>
+      <c r="E170" s="0" t="inlineStr"/>
+      <c r="F170" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="171">
-      <c r="A171" s="0">
-        <v>4545</v>
-      </c>
-      <c r="B171" s="1">
-        <v>46122</v>
-      </c>
-      <c r="C171" s="2">
-        <v>1178.03</v>
-      </c>
-      <c r="D171" s="0" t="inlineStr">
-        <is>
-          <t>2O260402157</t>
-        </is>
-      </c>
-      <c r="E171" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F171" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A171" s="0"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="0" t="inlineStr"/>
+      <c r="E171" s="0" t="inlineStr"/>
+      <c r="F171" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="172">
-      <c r="A172" s="0">
-        <v>4561</v>
-      </c>
-      <c r="B172" s="1">
-        <v>46123</v>
-      </c>
-      <c r="C172" s="2">
-        <v>-120</v>
-      </c>
-      <c r="D172" s="0" t="inlineStr">
-        <is>
-          <t>3367O5</t>
-        </is>
-      </c>
-      <c r="E172" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F172" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A172" s="0"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="0" t="inlineStr"/>
+      <c r="E172" s="0" t="inlineStr"/>
+      <c r="F172" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="173">
-      <c r="A173" s="0">
-        <v>4549</v>
-      </c>
-      <c r="B173" s="1">
-        <v>46123</v>
-      </c>
-      <c r="C173" s="2">
-        <v>600</v>
-      </c>
-      <c r="D173" s="0" t="inlineStr">
-        <is>
-          <t>20260049</t>
-        </is>
-      </c>
-      <c r="E173" s="0" t="inlineStr">
-        <is>
-          <t>SK8009000000000000000010</t>
-        </is>
-      </c>
-      <c r="F173" s="0" t="inlineStr">
-        <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
-        </is>
-      </c>
+      <c r="A173" s="0"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="0" t="inlineStr"/>
+      <c r="E173" s="0" t="inlineStr"/>
+      <c r="F173" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="174">
-      <c r="A174" s="0">
-        <v>4558</v>
-      </c>
-      <c r="B174" s="1">
-        <v>46125</v>
-      </c>
-      <c r="C174" s="2">
-        <v>837.32</v>
-      </c>
-      <c r="D174" s="0" t="inlineStr">
-        <is>
-          <t>2O260408168</t>
-        </is>
-      </c>
-      <c r="E174" s="0" t="inlineStr">
-        <is>
-          <t>CZ2601000000000000000019</t>
-        </is>
-      </c>
-      <c r="F174" s="0" t="inlineStr">
-        <is>
-          <t>Alza.cz a.s.</t>
-        </is>
-      </c>
+      <c r="A174" s="0"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="0" t="inlineStr"/>
+      <c r="E174" s="0" t="inlineStr"/>
+      <c r="F174" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="175">
-      <c r="A175" s="0">
-        <v>4566</v>
-      </c>
-      <c r="B175" s="1">
-        <v>46126</v>
-      </c>
-      <c r="C175" s="2">
-        <v>1566.23</v>
-      </c>
-      <c r="D175" s="0" t="inlineStr">
-        <is>
-          <t>2O260410176</t>
-        </is>
-      </c>
-      <c r="E175" s="0" t="inlineStr">
-        <is>
-          <t>CZ2601000000000000000019</t>
-        </is>
-      </c>
-      <c r="F175" s="0" t="inlineStr">
-        <is>
-          <t>Alza.cz a.s.</t>
-        </is>
-      </c>
+      <c r="A175" s="0"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="0" t="inlineStr"/>
+      <c r="E175" s="0" t="inlineStr"/>
+      <c r="F175" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="176">
-      <c r="A176" s="0">
-        <v>4556</v>
-      </c>
-      <c r="B176" s="1">
-        <v>46126</v>
-      </c>
-      <c r="C176" s="2">
-        <v>997.42</v>
-      </c>
-      <c r="D176" s="0" t="inlineStr">
-        <is>
-          <t>UHRADA50</t>
-        </is>
-      </c>
-      <c r="E176" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F176" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A176" s="0"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="0" t="inlineStr"/>
+      <c r="E176" s="0" t="inlineStr"/>
+      <c r="F176" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="177">
-      <c r="A177" s="0">
-        <v>4568</v>
-      </c>
-      <c r="B177" s="1">
-        <v>46128</v>
-      </c>
-      <c r="C177" s="2">
-        <v>663.85</v>
-      </c>
-      <c r="D177" s="0" t="inlineStr">
-        <is>
-          <t>UHRADA28</t>
-        </is>
-      </c>
-      <c r="E177" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F177" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A177" s="0"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="0" t="inlineStr"/>
+      <c r="E177" s="0" t="inlineStr"/>
+      <c r="F177" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="178">
-      <c r="A178" s="0">
-        <v>4539</v>
-      </c>
-      <c r="B178" s="1">
-        <v>46129</v>
-      </c>
-      <c r="C178" s="2">
-        <v>553.82</v>
-      </c>
-      <c r="D178" s="0" t="inlineStr">
-        <is>
-          <t>20260401153</t>
-        </is>
-      </c>
-      <c r="E178" s="0" t="inlineStr">
-        <is>
-          <t>GB46BARC00000000000020</t>
-        </is>
-      </c>
-      <c r="F178" s="0" t="inlineStr">
-        <is>
-          <t>British Airways</t>
-        </is>
-      </c>
+      <c r="A178" s="0"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="0" t="inlineStr"/>
+      <c r="E178" s="0" t="inlineStr"/>
+      <c r="F178" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="179">
-      <c r="A179" s="0">
-        <v>4577</v>
-      </c>
-      <c r="B179" s="1">
-        <v>46130</v>
-      </c>
-      <c r="C179" s="2">
-        <v>-45.9</v>
-      </c>
-      <c r="D179" s="0" t="inlineStr">
-        <is>
-          <t>3163591O</t>
-        </is>
-      </c>
-      <c r="E179" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F179" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A179" s="0"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="0" t="inlineStr"/>
+      <c r="E179" s="0" t="inlineStr"/>
+      <c r="F179" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="180">
-      <c r="A180" s="0">
-        <v>4574</v>
-      </c>
-      <c r="B180" s="1">
-        <v>46131</v>
-      </c>
-      <c r="C180" s="2">
-        <v>1326.23</v>
-      </c>
-      <c r="D180" s="0" t="inlineStr">
-        <is>
-          <t>UHRADA71</t>
-        </is>
-      </c>
-      <c r="E180" s="0" t="inlineStr">
-        <is>
-          <t>SK8009000000000000000010</t>
-        </is>
-      </c>
-      <c r="F180" s="0" t="inlineStr">
-        <is>
-          <t>Ing. Pavol Vnuk - NORPAL</t>
-        </is>
-      </c>
+      <c r="A180" s="0"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="0" t="inlineStr"/>
+      <c r="E180" s="0" t="inlineStr"/>
+      <c r="F180" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="181">
-      <c r="A181" s="0">
-        <v>4534</v>
-      </c>
-      <c r="B181" s="1">
-        <v>46132</v>
-      </c>
-      <c r="C181" s="2">
-        <v>-663.19</v>
-      </c>
-      <c r="D181" s="0" t="inlineStr">
-        <is>
-          <t>20260330148</t>
-        </is>
-      </c>
-      <c r="E181" s="0" t="inlineStr">
-        <is>
-          <t>SK9509000000000000000006</t>
-        </is>
-      </c>
-      <c r="F181" s="0" t="inlineStr">
-        <is>
-          <t>KROS a.s.</t>
-        </is>
-      </c>
+      <c r="A181" s="0"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="0" t="inlineStr"/>
+      <c r="E181" s="0" t="inlineStr"/>
+      <c r="F181" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="182">
-      <c r="A182" s="0">
-        <v>4547</v>
-      </c>
-      <c r="B182" s="1">
-        <v>46132</v>
-      </c>
-      <c r="C182" s="2">
-        <v>295.27</v>
-      </c>
-      <c r="D182" s="0" t="inlineStr">
-        <is>
-          <t>20260402158</t>
-        </is>
-      </c>
-      <c r="E182" s="0" t="inlineStr">
-        <is>
-          <t>SK3309000000000000000011</t>
-        </is>
-      </c>
-      <c r="F182" s="0" t="inlineStr">
-        <is>
-          <t>Flux a.s.</t>
-        </is>
-      </c>
+      <c r="A182" s="0"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="0" t="inlineStr"/>
+      <c r="E182" s="0" t="inlineStr"/>
+      <c r="F182" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="183">
-      <c r="A183" s="0">
-        <v>4579</v>
-      </c>
-      <c r="B183" s="1">
-        <v>46132</v>
-      </c>
-      <c r="C183" s="2">
-        <v>-7.5</v>
-      </c>
-      <c r="D183" s="0" t="inlineStr">
-        <is>
-          <t>POPLATOK 04/2026</t>
-        </is>
-      </c>
-      <c r="F183" s="0" t="inlineStr">
-        <is>
-          <t>Mesačný poplatok za účet</t>
-        </is>
-      </c>
+      <c r="A183" s="0"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="0" t="inlineStr"/>
+      <c r="F183" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
